--- a/artfynd/A 29667-2024 artfynd.xlsx
+++ b/artfynd/A 29667-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762179</v>
       </c>
       <c r="B2" t="n">
-        <v>92061</v>
+        <v>92063</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136762181</v>
       </c>
       <c r="B3" t="n">
-        <v>89472</v>
+        <v>89474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762172</v>
       </c>
       <c r="B4" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762174</v>
       </c>
       <c r="B5" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762176</v>
       </c>
       <c r="B6" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762177</v>
       </c>
       <c r="B7" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762178</v>
       </c>
       <c r="B8" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762180</v>
       </c>
       <c r="B9" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762188</v>
       </c>
       <c r="B10" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762185</v>
       </c>
       <c r="B11" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762171</v>
       </c>
       <c r="B12" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762182</v>
       </c>
       <c r="B13" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762187</v>
       </c>
       <c r="B14" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762170</v>
       </c>
       <c r="B16" t="n">
-        <v>92336</v>
+        <v>92338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762175</v>
       </c>
       <c r="B17" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 29667-2024 artfynd.xlsx
+++ b/artfynd/A 29667-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762179</v>
       </c>
       <c r="B2" t="n">
-        <v>92063</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136762181</v>
       </c>
       <c r="B3" t="n">
-        <v>89474</v>
+        <v>89476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762172</v>
       </c>
       <c r="B4" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762174</v>
       </c>
       <c r="B5" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762176</v>
       </c>
       <c r="B6" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762177</v>
       </c>
       <c r="B7" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762178</v>
       </c>
       <c r="B8" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762180</v>
       </c>
       <c r="B9" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762188</v>
       </c>
       <c r="B10" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762185</v>
       </c>
       <c r="B11" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762171</v>
       </c>
       <c r="B12" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762182</v>
       </c>
       <c r="B13" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762187</v>
       </c>
       <c r="B14" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136762168</v>
       </c>
       <c r="B15" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762170</v>
       </c>
       <c r="B16" t="n">
-        <v>92338</v>
+        <v>92340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762175</v>
       </c>
       <c r="B17" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136762169</v>
       </c>
       <c r="B18" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136762183</v>
       </c>
       <c r="B19" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136762189</v>
       </c>
       <c r="B20" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136762173</v>
       </c>
       <c r="B21" t="n">
-        <v>79732</v>
+        <v>79736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136762184</v>
       </c>
       <c r="B22" t="n">
-        <v>79732</v>
+        <v>79736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136762191</v>
       </c>
       <c r="B23" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136762190</v>
       </c>
       <c r="B24" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 29667-2024 artfynd.xlsx
+++ b/artfynd/A 29667-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762179</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136762181</v>
       </c>
       <c r="B3" t="n">
-        <v>89476</v>
+        <v>89478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762172</v>
       </c>
       <c r="B4" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762174</v>
       </c>
       <c r="B5" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762176</v>
       </c>
       <c r="B6" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762177</v>
       </c>
       <c r="B7" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762178</v>
       </c>
       <c r="B8" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762180</v>
       </c>
       <c r="B9" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762188</v>
       </c>
       <c r="B10" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762185</v>
       </c>
       <c r="B11" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762171</v>
       </c>
       <c r="B12" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762182</v>
       </c>
       <c r="B13" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762187</v>
       </c>
       <c r="B14" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136762168</v>
       </c>
       <c r="B15" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762170</v>
       </c>
       <c r="B16" t="n">
-        <v>92340</v>
+        <v>92342</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762175</v>
       </c>
       <c r="B17" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136762169</v>
       </c>
       <c r="B18" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136762183</v>
       </c>
       <c r="B19" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136762189</v>
       </c>
       <c r="B20" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136762173</v>
       </c>
       <c r="B21" t="n">
-        <v>79736</v>
+        <v>79738</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136762184</v>
       </c>
       <c r="B22" t="n">
-        <v>79736</v>
+        <v>79738</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136762191</v>
       </c>
       <c r="B23" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136762190</v>
       </c>
       <c r="B24" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 29667-2024 artfynd.xlsx
+++ b/artfynd/A 29667-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762179</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92068</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136762181</v>
       </c>
       <c r="B3" t="n">
-        <v>89478</v>
+        <v>89479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762172</v>
       </c>
       <c r="B4" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762174</v>
       </c>
       <c r="B5" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762176</v>
       </c>
       <c r="B6" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762177</v>
       </c>
       <c r="B7" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762178</v>
       </c>
       <c r="B8" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762180</v>
       </c>
       <c r="B9" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762188</v>
       </c>
       <c r="B10" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762185</v>
       </c>
       <c r="B11" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762171</v>
       </c>
       <c r="B12" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762182</v>
       </c>
       <c r="B13" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762187</v>
       </c>
       <c r="B14" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136762168</v>
       </c>
       <c r="B15" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762170</v>
       </c>
       <c r="B16" t="n">
-        <v>92342</v>
+        <v>92343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762175</v>
       </c>
       <c r="B17" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136762169</v>
       </c>
       <c r="B18" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136762183</v>
       </c>
       <c r="B19" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136762189</v>
       </c>
       <c r="B20" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136762173</v>
       </c>
       <c r="B21" t="n">
-        <v>79738</v>
+        <v>79739</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136762184</v>
       </c>
       <c r="B22" t="n">
-        <v>79738</v>
+        <v>79739</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136762191</v>
       </c>
       <c r="B23" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136762190</v>
       </c>
       <c r="B24" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 29667-2024 artfynd.xlsx
+++ b/artfynd/A 29667-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762179</v>
       </c>
       <c r="B2" t="n">
-        <v>92068</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136762181</v>
       </c>
       <c r="B3" t="n">
-        <v>89479</v>
+        <v>89485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762172</v>
       </c>
       <c r="B4" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762174</v>
       </c>
       <c r="B5" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762176</v>
       </c>
       <c r="B6" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762177</v>
       </c>
       <c r="B7" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762178</v>
       </c>
       <c r="B8" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762180</v>
       </c>
       <c r="B9" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762188</v>
       </c>
       <c r="B10" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762185</v>
       </c>
       <c r="B11" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762171</v>
       </c>
       <c r="B12" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762182</v>
       </c>
       <c r="B13" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762187</v>
       </c>
       <c r="B14" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762170</v>
       </c>
       <c r="B16" t="n">
-        <v>92343</v>
+        <v>92349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762175</v>
       </c>
       <c r="B17" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 29667-2024 artfynd.xlsx
+++ b/artfynd/A 29667-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762179</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136762181</v>
       </c>
       <c r="B3" t="n">
-        <v>89485</v>
+        <v>89489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762172</v>
       </c>
       <c r="B4" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762174</v>
       </c>
       <c r="B5" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762176</v>
       </c>
       <c r="B6" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762177</v>
       </c>
       <c r="B7" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762178</v>
       </c>
       <c r="B8" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762180</v>
       </c>
       <c r="B9" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762188</v>
       </c>
       <c r="B10" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762185</v>
       </c>
       <c r="B11" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762171</v>
       </c>
       <c r="B12" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762182</v>
       </c>
       <c r="B13" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762187</v>
       </c>
       <c r="B14" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136762168</v>
       </c>
       <c r="B15" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762170</v>
       </c>
       <c r="B16" t="n">
-        <v>92349</v>
+        <v>92353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762175</v>
       </c>
       <c r="B17" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136762169</v>
       </c>
       <c r="B18" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136762183</v>
       </c>
       <c r="B19" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136762189</v>
       </c>
       <c r="B20" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136762173</v>
       </c>
       <c r="B21" t="n">
-        <v>79739</v>
+        <v>79741</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136762184</v>
       </c>
       <c r="B22" t="n">
-        <v>79739</v>
+        <v>79741</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136762191</v>
       </c>
       <c r="B23" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136762190</v>
       </c>
       <c r="B24" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 29667-2024 artfynd.xlsx
+++ b/artfynd/A 29667-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762179</v>
       </c>
       <c r="B2" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136762181</v>
       </c>
       <c r="B3" t="n">
-        <v>89489</v>
+        <v>89491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762172</v>
       </c>
       <c r="B4" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762174</v>
       </c>
       <c r="B5" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762176</v>
       </c>
       <c r="B6" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762177</v>
       </c>
       <c r="B7" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762178</v>
       </c>
       <c r="B8" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762180</v>
       </c>
       <c r="B9" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762188</v>
       </c>
       <c r="B10" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762185</v>
       </c>
       <c r="B11" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762171</v>
       </c>
       <c r="B12" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762182</v>
       </c>
       <c r="B13" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762187</v>
       </c>
       <c r="B14" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136762168</v>
       </c>
       <c r="B15" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762170</v>
       </c>
       <c r="B16" t="n">
-        <v>92353</v>
+        <v>92355</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762175</v>
       </c>
       <c r="B17" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136762169</v>
       </c>
       <c r="B18" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136762183</v>
       </c>
       <c r="B19" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136762189</v>
       </c>
       <c r="B20" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136762173</v>
       </c>
       <c r="B21" t="n">
-        <v>79741</v>
+        <v>79744</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136762184</v>
       </c>
       <c r="B22" t="n">
-        <v>79741</v>
+        <v>79744</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136762191</v>
       </c>
       <c r="B23" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136762190</v>
       </c>
       <c r="B24" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 29667-2024 artfynd.xlsx
+++ b/artfynd/A 29667-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762179</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136762181</v>
       </c>
       <c r="B3" t="n">
-        <v>89491</v>
+        <v>89504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762172</v>
       </c>
       <c r="B4" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762174</v>
       </c>
       <c r="B5" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762176</v>
       </c>
       <c r="B6" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762177</v>
       </c>
       <c r="B7" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762178</v>
       </c>
       <c r="B8" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762180</v>
       </c>
       <c r="B9" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762188</v>
       </c>
       <c r="B10" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762185</v>
       </c>
       <c r="B11" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762171</v>
       </c>
       <c r="B12" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762182</v>
       </c>
       <c r="B13" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762187</v>
       </c>
       <c r="B14" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136762168</v>
       </c>
       <c r="B15" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762170</v>
       </c>
       <c r="B16" t="n">
-        <v>92355</v>
+        <v>92368</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762175</v>
       </c>
       <c r="B17" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136762169</v>
       </c>
       <c r="B18" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136762183</v>
       </c>
       <c r="B19" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136762189</v>
       </c>
       <c r="B20" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136762173</v>
       </c>
       <c r="B21" t="n">
-        <v>79744</v>
+        <v>79757</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136762184</v>
       </c>
       <c r="B22" t="n">
-        <v>79744</v>
+        <v>79757</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136762191</v>
       </c>
       <c r="B23" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136762190</v>
       </c>
       <c r="B24" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136762186</v>
       </c>
       <c r="B25" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 29667-2024 artfynd.xlsx
+++ b/artfynd/A 29667-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762179</v>
       </c>
       <c r="B2" t="n">
-        <v>92093</v>
+        <v>92095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136762181</v>
       </c>
       <c r="B3" t="n">
-        <v>89504</v>
+        <v>89506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762172</v>
       </c>
       <c r="B4" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762174</v>
       </c>
       <c r="B5" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762176</v>
       </c>
       <c r="B6" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762177</v>
       </c>
       <c r="B7" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762178</v>
       </c>
       <c r="B8" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762180</v>
       </c>
       <c r="B9" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762188</v>
       </c>
       <c r="B10" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762185</v>
       </c>
       <c r="B11" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762171</v>
       </c>
       <c r="B12" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762182</v>
       </c>
       <c r="B13" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762187</v>
       </c>
       <c r="B14" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136762168</v>
       </c>
       <c r="B15" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762170</v>
       </c>
       <c r="B16" t="n">
-        <v>92368</v>
+        <v>92370</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762175</v>
       </c>
       <c r="B17" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136762169</v>
       </c>
       <c r="B18" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136762183</v>
       </c>
       <c r="B19" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136762189</v>
       </c>
       <c r="B20" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136762173</v>
       </c>
       <c r="B21" t="n">
-        <v>79757</v>
+        <v>79759</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136762184</v>
       </c>
       <c r="B22" t="n">
-        <v>79757</v>
+        <v>79759</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136762191</v>
       </c>
       <c r="B23" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136762190</v>
       </c>
       <c r="B24" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136762186</v>
       </c>
       <c r="B25" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 29667-2024 artfynd.xlsx
+++ b/artfynd/A 29667-2024 artfynd.xlsx
@@ -3289,16 +3289,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vimyrorna, Mpd</t>

--- a/artfynd/A 29667-2024 artfynd.xlsx
+++ b/artfynd/A 29667-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762179</v>
       </c>
       <c r="B2" t="n">
-        <v>92095</v>
+        <v>92098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136762181</v>
       </c>
       <c r="B3" t="n">
-        <v>89506</v>
+        <v>89509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762172</v>
       </c>
       <c r="B4" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762174</v>
       </c>
       <c r="B5" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762176</v>
       </c>
       <c r="B6" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762177</v>
       </c>
       <c r="B7" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762178</v>
       </c>
       <c r="B8" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762180</v>
       </c>
       <c r="B9" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762188</v>
       </c>
       <c r="B10" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762185</v>
       </c>
       <c r="B11" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762171</v>
       </c>
       <c r="B12" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762182</v>
       </c>
       <c r="B13" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762187</v>
       </c>
       <c r="B14" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762170</v>
       </c>
       <c r="B16" t="n">
-        <v>92370</v>
+        <v>92373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762175</v>
       </c>
       <c r="B17" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 29667-2024 artfynd.xlsx
+++ b/artfynd/A 29667-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762179</v>
       </c>
       <c r="B2" t="n">
-        <v>92098</v>
+        <v>92108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136762181</v>
       </c>
       <c r="B3" t="n">
-        <v>89509</v>
+        <v>89519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762172</v>
       </c>
       <c r="B4" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762174</v>
       </c>
       <c r="B5" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762176</v>
       </c>
       <c r="B6" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762177</v>
       </c>
       <c r="B7" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762178</v>
       </c>
       <c r="B8" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762180</v>
       </c>
       <c r="B9" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762188</v>
       </c>
       <c r="B10" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762185</v>
       </c>
       <c r="B11" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762171</v>
       </c>
       <c r="B12" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762182</v>
       </c>
       <c r="B13" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762187</v>
       </c>
       <c r="B14" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136762168</v>
       </c>
       <c r="B15" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762170</v>
       </c>
       <c r="B16" t="n">
-        <v>92373</v>
+        <v>92383</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762175</v>
       </c>
       <c r="B17" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136762169</v>
       </c>
       <c r="B18" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136762183</v>
       </c>
       <c r="B19" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136762189</v>
       </c>
       <c r="B20" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136762173</v>
       </c>
       <c r="B21" t="n">
-        <v>79759</v>
+        <v>79769</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136762184</v>
       </c>
       <c r="B22" t="n">
-        <v>79759</v>
+        <v>79769</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136762191</v>
       </c>
       <c r="B23" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136762190</v>
       </c>
       <c r="B24" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136762186</v>
       </c>
       <c r="B25" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 29667-2024 artfynd.xlsx
+++ b/artfynd/A 29667-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762179</v>
       </c>
       <c r="B2" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136762181</v>
       </c>
       <c r="B3" t="n">
-        <v>89519</v>
+        <v>89520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762172</v>
       </c>
       <c r="B4" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762174</v>
       </c>
       <c r="B5" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762176</v>
       </c>
       <c r="B6" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762177</v>
       </c>
       <c r="B7" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762178</v>
       </c>
       <c r="B8" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762180</v>
       </c>
       <c r="B9" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762188</v>
       </c>
       <c r="B10" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762185</v>
       </c>
       <c r="B11" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762171</v>
       </c>
       <c r="B12" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762182</v>
       </c>
       <c r="B13" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762187</v>
       </c>
       <c r="B14" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762170</v>
       </c>
       <c r="B16" t="n">
-        <v>92383</v>
+        <v>92384</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762175</v>
       </c>
       <c r="B17" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 29667-2024 artfynd.xlsx
+++ b/artfynd/A 29667-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762179</v>
       </c>
       <c r="B2" t="n">
-        <v>92109</v>
+        <v>92112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136762181</v>
       </c>
       <c r="B3" t="n">
-        <v>89520</v>
+        <v>89523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762172</v>
       </c>
       <c r="B4" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762174</v>
       </c>
       <c r="B5" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762176</v>
       </c>
       <c r="B6" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762177</v>
       </c>
       <c r="B7" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762178</v>
       </c>
       <c r="B8" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762180</v>
       </c>
       <c r="B9" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762188</v>
       </c>
       <c r="B10" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762185</v>
       </c>
       <c r="B11" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762171</v>
       </c>
       <c r="B12" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762182</v>
       </c>
       <c r="B13" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762187</v>
       </c>
       <c r="B14" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136762168</v>
       </c>
       <c r="B15" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762170</v>
       </c>
       <c r="B16" t="n">
-        <v>92384</v>
+        <v>92387</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762175</v>
       </c>
       <c r="B17" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136762169</v>
       </c>
       <c r="B18" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136762183</v>
       </c>
       <c r="B19" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136762189</v>
       </c>
       <c r="B20" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136762173</v>
       </c>
       <c r="B21" t="n">
-        <v>79769</v>
+        <v>79772</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136762184</v>
       </c>
       <c r="B22" t="n">
-        <v>79769</v>
+        <v>79772</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136762191</v>
       </c>
       <c r="B23" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136762190</v>
       </c>
       <c r="B24" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136762186</v>
       </c>
       <c r="B25" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 29667-2024 artfynd.xlsx
+++ b/artfynd/A 29667-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762179</v>
       </c>
       <c r="B2" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762172</v>
       </c>
       <c r="B4" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762174</v>
       </c>
       <c r="B5" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762176</v>
       </c>
       <c r="B6" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762177</v>
       </c>
       <c r="B7" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762178</v>
       </c>
       <c r="B8" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762180</v>
       </c>
       <c r="B9" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762188</v>
       </c>
       <c r="B10" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762185</v>
       </c>
       <c r="B11" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762171</v>
       </c>
       <c r="B12" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762182</v>
       </c>
       <c r="B13" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762187</v>
       </c>
       <c r="B14" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762170</v>
       </c>
       <c r="B16" t="n">
-        <v>92387</v>
+        <v>92389</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762175</v>
       </c>
       <c r="B17" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
